--- a/Hoadon/HD2026/HDRa/5/001065010300_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDRa/5/001065010300_HDDienTuMayTinhTien.xlsx
@@ -3656,6 +3656,1358 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H57" s="7"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>Ấp Phước Lợi, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K57" s="6" t="inlineStr">
+        <is>
+          <t>036193020990</t>
+        </is>
+      </c>
+      <c r="L57" s="13"/>
+      <c r="M57" s="13"/>
+      <c r="N57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O57" s="13" t="n">
+        <v>2692000.0</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H58" s="7"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>Ấp Tân Phước, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>077178000236</t>
+        </is>
+      </c>
+      <c r="L58" s="13"/>
+      <c r="M58" s="13"/>
+      <c r="N58" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O58" s="13" t="n">
+        <v>1.03092E7</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H59" s="7"/>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>Tạp Hóa KIM NHUNG</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>G37, Tổ 3 Ấp Phước Tân, Xã Long Hải, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>036173010447</t>
+        </is>
+      </c>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>2381000.0</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>077191003978</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>TẠP HÓA NGỌC ÁNH</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>F47, Tổ 11, Ấp Phước Lợi, Xã Long Hải, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>077191003978</t>
+        </is>
+      </c>
+      <c r="L60" s="13"/>
+      <c r="M60" s="13"/>
+      <c r="N60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O60" s="13" t="n">
+        <v>8495000.0</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="13"/>
+      <c r="M61" s="13"/>
+      <c r="N61" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O61" s="13" t="n">
+        <v>4900000.0</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>077092001081</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>HKD CỬA HÀNG TIỆN LỢI NAM HẰNG</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>E07, Tổ 6 , Ấp Phước Thiện, xã Long Hải, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>077092001081</t>
+        </is>
+      </c>
+      <c r="L62" s="13"/>
+      <c r="M62" s="13"/>
+      <c r="N62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>4758400.0</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H63" s="7"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>051173003094</t>
+        </is>
+      </c>
+      <c r="L63" s="13"/>
+      <c r="M63" s="13"/>
+      <c r="N63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>4688000.0</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H64" s="7"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 8 Ấp Hải Sơn, Xã Long Hải, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>036181020971</t>
+        </is>
+      </c>
+      <c r="L64" s="13"/>
+      <c r="M64" s="13"/>
+      <c r="N64" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>2257000.0</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>077099003775</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH PHỤNG GAMING</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>Số 16, đường Huỳnh Khương An, tổ 1, ấp Phước Lâm, xã Long Hải, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>077099003775</t>
+        </is>
+      </c>
+      <c r="L65" s="13"/>
+      <c r="M65" s="13"/>
+      <c r="N65" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>2065000.0</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H66" s="7"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>Ấp Phước Tân, Xã Long Hải, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>051184004124</t>
+        </is>
+      </c>
+      <c r="L66" s="13"/>
+      <c r="M66" s="13"/>
+      <c r="N66" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>3894000.0</v>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H67" s="7"/>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH PHẠM PHI LONG</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>Số 4, Tổ 6, ấp Phước Lâm, Xã Long Hải, TP Hồ Chí Minh Việt Nam</t>
+        </is>
+      </c>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>077096009452</t>
+        </is>
+      </c>
+      <c r="L67" s="13"/>
+      <c r="M67" s="13"/>
+      <c r="N67" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O67" s="13" t="n">
+        <v>1311000.0</v>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>052087015395</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>HDK LÊ GIA</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 2, ấp Tân Phước, Xã Long Hải, Tp Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>052087015395</t>
+        </is>
+      </c>
+      <c r="L68" s="13"/>
+      <c r="M68" s="13"/>
+      <c r="N68" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O68" s="13" t="n">
+        <v>2885000.0</v>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>077185004699</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>Trần Thị Bông</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>B02-293 Chợ Phước Tỉnh, xã Long Hải, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K69" s="6"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+      <c r="N69" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O69" s="13" t="n">
+        <v>4255000.0</v>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H70" s="7"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>Tổ 8 Ấp Hải Sơn, Xã Long Hải, Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K70" s="6" t="inlineStr">
+        <is>
+          <t>036181020971</t>
+        </is>
+      </c>
+      <c r="L70" s="13"/>
+      <c r="M70" s="13"/>
+      <c r="N70" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O70" s="13" t="n">
+        <v>1448000.0</v>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H71" s="7"/>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>QUÁN NHẬU HAI CÔ TIÊN</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>Âp Tân Phước, Xã Long Hải, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K71" s="6" t="inlineStr">
+        <is>
+          <t>077171000910</t>
+        </is>
+      </c>
+      <c r="L71" s="13"/>
+      <c r="M71" s="13"/>
+      <c r="N71" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O71" s="13" t="n">
+        <v>5936000.0</v>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>66.0</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H72" s="7"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>Ấp Phước Bình, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>077188001351</t>
+        </is>
+      </c>
+      <c r="L72" s="13"/>
+      <c r="M72" s="13"/>
+      <c r="N72" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O72" s="13" t="n">
+        <v>5808000.0</v>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H73" s="7"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>D13 Tổ 7 Ấp Phước Thái, xã Long Hải, Tp Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>077182003068</t>
+        </is>
+      </c>
+      <c r="L73" s="13"/>
+      <c r="M73" s="13"/>
+      <c r="N73" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O73" s="13" t="n">
+        <v>6240000.0</v>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>68.0</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H74" s="7"/>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>TẠP HÓA VINH</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>B16, Tổ 12 Ấp Phước Bình, Xã Long Hải, TP Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>075070001309</t>
+        </is>
+      </c>
+      <c r="L74" s="13"/>
+      <c r="M74" s="13"/>
+      <c r="N74" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O74" s="13" t="n">
+        <v>5160000.0</v>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>3500719172</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH KARAOKE KEN</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>F14 đường Hương lộ 5, Tổ 1, ấp Phước Lợi, Xã Phước Tỉnh, Huyện Long Điền, Bà Rịa - Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>077078001863</t>
+        </is>
+      </c>
+      <c r="L75" s="13"/>
+      <c r="M75" s="13"/>
+      <c r="N75" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O75" s="13" t="n">
+        <v>1.056E7</v>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>C26MHM</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>001065010300</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>CỬA HÀNG BIA, NƯỚC NGỌT HÙNG MẠNH</t>
+        </is>
+      </c>
+      <c r="H76" s="7"/>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>Tạp Hóa HẢI HƯNG</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>F83, Tổ 13, Ấp Phước Lợi, Xã Long Hải, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K76" s="6" t="inlineStr">
+        <is>
+          <t>077079000057</t>
+        </is>
+      </c>
+      <c r="L76" s="13"/>
+      <c r="M76" s="13"/>
+      <c r="N76" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O76" s="13" t="n">
+        <v>7872000.0</v>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>

--- a/Hoadon/HD2026/HDRa/5/001065010300_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDRa/5/001065010300_HDDienTuMayTinhTien.xlsx
@@ -211,7 +211,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Từ ngày 01/05/2026 đến ngày 27/05/2026</t>
+          <t>Từ ngày 01/05/2026 đến ngày 31/05/2026</t>
         </is>
       </c>
     </row>
